--- a/新模板.xlsx
+++ b/新模板.xlsx
@@ -219,9 +219,10 @@
   <si>
     <t>1.检查：
   无。
-2.垃圾转运站0月00日污水转运情况：
-①.环境集团垃圾中转站污水外运量共计0吨：其中去环服0吨；去电厂0吨。
-②.环服公司接收垃圾中转站污水共计0吨：其中接收环境集团垃圾转运站：0吨；接收白云区：0吨；接收人和镇：0吨；太和镇：0吨；云埔街道：0吨；天河城管局：0吨；九龙镇：0吨。</t>
+2.垃圾转运站0月0日污水转运情况：
+广州市生活垃圾污水运输总量为0吨。
+①.按处置单位分：环服公司处置0吨，各资源热力电厂处置0吨。
+②.按运输单位分：环境集团承运0吨，社会单位承运0吨。</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1130,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1197,9 +1198,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2195,7 +2193,7 @@
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:7">
       <c r="A42" s="20"/>
-      <c r="B42" s="24"/>
+      <c r="B42" s="23"/>
       <c r="C42" s="11" t="s">
         <v>48</v>
       </c>
@@ -2206,7 +2204,7 @@
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:7">
       <c r="A43" s="20"/>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="24" t="s">
         <v>49</v>
       </c>
       <c r="C43" s="11" t="s">
@@ -2219,7 +2217,7 @@
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:7">
       <c r="A44" s="20"/>
-      <c r="B44" s="25"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="11" t="s">
         <v>51</v>
       </c>
@@ -2230,18 +2228,18 @@
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:7">
       <c r="A45" s="20"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="26" t="s">
+      <c r="B45" s="24"/>
+      <c r="C45" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="27"/>
+      <c r="D45" s="26"/>
       <c r="E45" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:7">
       <c r="A46" s="20"/>
-      <c r="B46" s="25"/>
+      <c r="B46" s="24"/>
       <c r="C46" s="11" t="s">
         <v>47</v>
       </c>
@@ -2251,72 +2249,72 @@
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:7">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:7">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:7">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:7">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="29" t="s">
         <v>56</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="31"/>
+      <c r="E50" s="30"/>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:7">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="34"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="33"/>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:7">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="29" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="31"/>
+      <c r="E52" s="30"/>
     </row>
     <row r="53" ht="148" customHeight="1" spans="1:7">
-      <c r="A53" s="35" t="s">
+      <c r="A53" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="37"/>
-      <c r="G53" s="38"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="36"/>
+      <c r="G53" s="37"/>
     </row>
     <row r="54" ht="14.25" customHeight="1"/>
     <row r="55" ht="14.25" customHeight="1" spans="1:7">
-      <c r="C55" s="38"/>
+      <c r="C55" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="47">

--- a/新模板.xlsx
+++ b/新模板.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57176\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="22188" windowHeight="9900"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +32,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
-  <si>
-    <t>广州环投2026-00-00生产运营情况</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+  <si>
+    <t>广州环投2026-10-06生产运营情况</t>
   </si>
   <si>
     <t>一、整体情况</t>
@@ -79,6 +84,9 @@
     <t>1.4-上网电量（万度）</t>
   </si>
   <si>
+    <t>1.5-飞灰外运资源化（吨）</t>
+  </si>
+  <si>
     <t>生
 物
 质
@@ -199,13 +207,34 @@
     <t>再生骨料1-2石</t>
   </si>
   <si>
+    <t>生活垃圾污水</t>
+  </si>
+  <si>
+    <t>运输</t>
+  </si>
+  <si>
+    <t>环境集团（吨）</t>
+  </si>
+  <si>
+    <t>社会单位（吨）</t>
+  </si>
+  <si>
+    <t>处置</t>
+  </si>
+  <si>
+    <t>环服公司（吨）</t>
+  </si>
+  <si>
+    <t>各资源热力电厂（吨）</t>
+  </si>
+  <si>
     <t>2、机炉运行情况</t>
   </si>
   <si>
-    <t>锅炉总数：00/00台运行正常（其中市内00/00台，市外0/0台）。</t>
-  </si>
-  <si>
-    <t>汽机总数：00/00台运行正常（其中市内00/00台，市外0/0台）。</t>
+    <t>锅炉总数：42/53台运行正常（其中市内37/44台，市外5/9台）。</t>
+  </si>
+  <si>
+    <t>汽机总数：25/32台运行正常（其中市内21/26台，市外4/6台）。</t>
   </si>
   <si>
     <t>二、异常情况（如道路交通安全情况）</t>
@@ -217,12 +246,10 @@
     <t>三、检查/专项</t>
   </si>
   <si>
-    <t>1.检查：
-  无。
-2.垃圾转运站0月0日污水转运情况：
-广州市生活垃圾污水运输总量为0吨。
-①.按处置单位分：环服公司处置0吨，各资源热力电厂处置0吨。
-②.按运输单位分：环境集团承运0吨，社会单位承运0吨。</t>
+    <t xml:space="preserve">检查：
+1.2026年10月6日上午，广州市生活废弃物管理中心四级调研员何淑坤带队赴环投花城公司开展国庆期间安全生产督导检查。
+2.2026年10月6日上午，市城管局执法处吴宗飞副处长带队赴从化废旧塑料回收项目施工现场进行安全生产检查，从化区城管局冯榕森副局长陪同检查。
+</t>
   </si>
 </sst>
 </file>
@@ -622,7 +649,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -644,6 +671,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -659,6 +706,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -692,6 +763,19 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -710,6 +794,65 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -720,31 +863,29 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top/>
@@ -767,22 +908,29 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -809,25 +957,23 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -853,12 +999,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -868,11 +1010,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="medium">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -982,266 +1122,261 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="47">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1696,632 +1831,692 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="9.65" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr defaultColWidth="9.64814814814815" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.51666666666667" customWidth="1"/>
-    <col min="2" max="2" width="10.2583333333333" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="26.3083333333333" customWidth="1"/>
-    <col min="5" max="5" width="12.1833333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.2583333333333" customWidth="1"/>
-    <col min="7" max="8" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="4.51851851851852" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.2592592592593" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8796296296296" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.3055555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1851851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.2592592592593" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="41.1" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="2" t="str">
+        <v>广州环投2026-00-00生产运营情况</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" ht="20.25" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="9" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:5">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:5">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="10" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="10" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:6">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="10" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:6">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:6">
+      <c r="A19" s="14"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:6">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
+      <c r="D19" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:6">
+      <c r="A20" s="14"/>
+      <c r="B20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:6">
+      <c r="A21" s="14"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:6">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:6">
+      <c r="A23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:6">
+      <c r="A24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:6">
+      <c r="A25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:6">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:6">
+      <c r="A27" s="14"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:6">
+      <c r="A28" s="14"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="E28" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:6">
+      <c r="A29" s="14"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="24"/>
+      <c r="E29" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:6">
+      <c r="A30" s="22"/>
+      <c r="B30" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:6">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:6">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:6">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:6">
-      <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="5" t="s">
+      <c r="C30" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:6">
+      <c r="A31" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:6">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:6">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:6">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:6">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:6">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:6">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:6">
-      <c r="A30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:6">
-      <c r="A31" s="12"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="8">
-        <v>0</v>
-      </c>
-      <c r="F31" s="13"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:6">
-      <c r="A32" s="12"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="24"/>
+      <c r="E32" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="27"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:7">
+      <c r="A33" s="14"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="8">
-        <v>0</v>
-      </c>
-      <c r="F32" s="13"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:7">
-      <c r="A33" s="12"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="8">
-        <v>0</v>
-      </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16"/>
+      <c r="E33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="27"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:7">
-      <c r="A34" s="12"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="11" t="s">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="8">
-        <v>0</v>
-      </c>
-      <c r="F34" s="15"/>
+      <c r="E34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="27"/>
+      <c r="G34"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:7">
-      <c r="A35" s="12"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="11" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="8">
-        <v>0</v>
-      </c>
-      <c r="F35" s="13"/>
+      <c r="E35" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:7">
-      <c r="A36" s="12"/>
-      <c r="B36" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="8">
-        <v>0</v>
-      </c>
+      <c r="A36" s="14"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="24"/>
+      <c r="E36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="27"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:7">
-      <c r="A37" s="17"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="8">
+      <c r="A37" s="14"/>
+      <c r="B37" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:7">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="D38" s="29"/>
+      <c r="E38" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:7">
+      <c r="A39" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1" spans="1:7">
-      <c r="A39" s="20"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="8">
+      <c r="D39" s="24"/>
+      <c r="E39" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:7">
-      <c r="A40" s="20"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="11" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="8">
+      <c r="D40" s="24"/>
+      <c r="E40" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:7">
-      <c r="A41" s="20"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="11" t="s">
+      <c r="A41" s="15"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="8">
+      <c r="D41" s="24"/>
+      <c r="E41" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:7">
-      <c r="A42" s="20"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="11" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="8">
+      <c r="D42" s="24"/>
+      <c r="E42" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:7">
-      <c r="A43" s="20"/>
-      <c r="B43" s="24" t="s">
+      <c r="A43" s="15"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="D43" s="24"/>
+      <c r="E43" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:7">
+      <c r="A44" s="15"/>
+      <c r="B44" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" spans="1:7">
-      <c r="A44" s="20"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="8">
+      <c r="D44" s="24"/>
+      <c r="E44" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:7">
-      <c r="A45" s="20"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="25" t="s">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="8">
+      <c r="D45" s="24"/>
+      <c r="E45" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:7">
-      <c r="A46" s="20"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="8">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="24"/>
+      <c r="E46" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:7">
-      <c r="A47" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="24"/>
+      <c r="E47" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:7">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+      <c r="B48" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="32"/>
+      <c r="E48" s="33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:7">
-      <c r="A49" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="35"/>
+      <c r="E49" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:7">
-      <c r="A50" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="30"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="35"/>
+      <c r="E50" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:7">
-      <c r="A51" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="33"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="35"/>
+      <c r="E51" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:7">
-      <c r="A52" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="30"/>
-    </row>
-    <row r="53" ht="148" customHeight="1" spans="1:7">
-      <c r="A53" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="36"/>
-      <c r="G53" s="37"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1" spans="1:7">
-      <c r="C55" s="37"/>
+      <c r="A52" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="38"/>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:7">
+      <c r="A53" s="39" t="str">
+        <v>锅炉总数：00/00台运行正常（其中市内00/00台，市外0/0台）。</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:7">
+      <c r="A54" s="39" t="str">
+        <v>汽机总数：00/00台运行正常（其中市内00/00台，市外0/0台）。</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="1:7">
+      <c r="A55" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:7">
+      <c r="A56" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="42"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:7">
+      <c r="A57" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" ht="148" customHeight="1" spans="1:7">
+      <c r="A58" s="43" t="str">
+        <v>检查：
+  无。</v>
+      </c>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="45"/>
+      <c r="G58" s="46"/>
+    </row>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1" spans="1:7">
+      <c r="C60" s="46"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="54">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
@@ -2330,7 +2525,7 @@
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
@@ -2342,29 +2537,37 @@
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A4:A22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A38:A46"/>
-    <mergeCell ref="B4:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B30:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C4:C12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A4:A23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="A39:A47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="B4:B19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C4:C13"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="F34:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.269444444444444" bottom="0.269444444444444" header="0" footer="0"/>
   <headerFooter/>

--- a/新模板.xlsx
+++ b/新模板.xlsx
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1" spans="1:7">
+    <row r="48" ht="22" customHeight="1" spans="1:7">
       <c r="A48" s="30" t="s">
         <v>54</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1" spans="1:7">
+    <row r="49" ht="22" customHeight="1" spans="1:7">
       <c r="A49" s="15"/>
       <c r="B49" s="15"/>
       <c r="C49" s="34" t="s">
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1" spans="1:7">
+    <row r="50" ht="22" customHeight="1" spans="1:7">
       <c r="A50" s="15"/>
       <c r="B50" s="10" t="s">
         <v>58</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1" spans="1:7">
+    <row r="51" ht="22" customHeight="1" spans="1:7">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="34" t="s">
